--- a/google_jobs.xlsx
+++ b/google_jobs.xlsx
@@ -14,11 +14,116 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="106">
+  <si>
+    <t>Logo</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
   <si>
     <t>Company</t>
   </si>
   <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2025/10/Grupo-Expertise-France-Groupe-AFD-Angola.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/04/Oportunidade-para-Formadores-Experientes-em-Angola.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/04/Empresa-abre-3-vagas-para-Recepcionistas-em-Luanda.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/04/HONLE-ELECTRIC-ANGOLA.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/04/vagas-para-secretaria-e-operadora-de-caixa.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/04/ISPOCA-Instituto-Superior-Politecnico-do-Cazenga.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/04/Vagsa-na-Refinaria-d-Lobito-.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2025/01/Contabilista-em-Angola-Ango-Emprego.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2025/03/Kelly-Moto-Angola.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2024/01/3-vagas-varias-vagas.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/04/6-Vagas-para-Area-Comercial-e-Vendas-Tecnicas-na-HonleElectric-Angola.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/04/Engenheiroa-Ambiental.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2024/12/Nors-logo-Angola.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/02/Ha-Vaga-Nova-Vaga.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/02/Nova-Vaga-de-Emprego.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2025/07/Recrutamento-Video-Maker-Ango-Emprego.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/02/empresa-tem-varias-vagas.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/04/Recruta-se-Tecnicoa-de-Controlo-de-Qualidade.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/01/Programadora-Full-Stack-Ango-Emprego-Emprego-em-Angola-Recrtuamento-em-Angola.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2025/12/director-comercial-Angola-Ango-Emprego-1.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/02/Oceaneering-Angola-Ango-Emprego.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2025/12/Supervisor-Angola-Ango-Emprego.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2025/01/NOX-Angola.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/02/DELOITTE-Candidatura-Espontanea.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2024/01/Bureau-Veritas.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2024/12/Access-Bank-Angola.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2025/01/Grupo-Mitrelli.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2024/05/Quintas-de-Jugais-logo-Ango-Emprego.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/05/SHIYDO-RESTAURANTE-Recruta-Chefe-de-Cozinha-em-Luanda-2.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/05/PROA-LDA.-Recruta-Coordenadora-de-Qualidade-e-Ambiente.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2024/06/Standard-Bank-Ango-Emprego.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/05/Vagas-no-Arreiou.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/angoemprego.com/wp-content/uploads/2026/05/Empresa-em-Angola-Recruta-Lideres-Seniores-%E2%80%93-10-Vagas-Disponiveis.jpg?resize=150%2C150&amp;ssl=1</t>
+  </si>
+  <si>
     <t>Oficial de Projeto (M/F)</t>
   </si>
   <si>
@@ -134,19 +239,119 @@
   </si>
   <si>
     <t>Técnico(a) de Risco de Mercado</t>
+  </si>
+  <si>
+    <t>Expertise Frnace</t>
+  </si>
+  <si>
+    <t>Empresa em Luanda</t>
+  </si>
+  <si>
+    <t>Honle Electric Angola</t>
+  </si>
+  <si>
+    <t>Empresa em Angola</t>
+  </si>
+  <si>
+    <t>ISPOCA</t>
+  </si>
+  <si>
+    <t>BING CHENG</t>
+  </si>
+  <si>
+    <t>Expertise France</t>
+  </si>
+  <si>
+    <t>Kelly Angola</t>
+  </si>
+  <si>
+    <t>HonleElectric Angola</t>
+  </si>
+  <si>
+    <t>Bom Jobs Recrutamento</t>
+  </si>
+  <si>
+    <t>Nors Group</t>
+  </si>
+  <si>
+    <t>Imbono</t>
+  </si>
+  <si>
+    <t>Digital Computer</t>
+  </si>
+  <si>
+    <t>Lucrus escola de vendas</t>
+  </si>
+  <si>
+    <t>Shalina Healthcare</t>
+  </si>
+  <si>
+    <t>Naniinvest</t>
+  </si>
+  <si>
+    <t>RADAR AO</t>
+  </si>
+  <si>
+    <t>Oceaneering</t>
+  </si>
+  <si>
+    <t>Dulceria Nacional LDA</t>
+  </si>
+  <si>
+    <t>Nox Angola</t>
+  </si>
+  <si>
+    <t>Deloitte Angola</t>
+  </si>
+  <si>
+    <t>Bureau Veritas North America</t>
+  </si>
+  <si>
+    <t>Access Bank Angola</t>
+  </si>
+  <si>
+    <t>Mitrelli</t>
+  </si>
+  <si>
+    <t>Quinta de Jugais Angola</t>
+  </si>
+  <si>
+    <t>SHIYDO RESTAURANTE, Lda.,</t>
+  </si>
+  <si>
+    <t>empresa PROA, LDA</t>
+  </si>
+  <si>
+    <t>ANCHICON-COMERCIO GERAL, LDA</t>
+  </si>
+  <si>
+    <t>Standard Bank Angola</t>
+  </si>
+  <si>
+    <t>ARREIOU</t>
+  </si>
+  <si>
+    <t>Agrovida ABC - Comércio Geral e Prestação de Serviços, Lda.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -166,13 +371,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -465,210 +676,491 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
+      <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
+      <c r="B24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
+      <c r="B32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>39</v>
+      <c r="B39" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A5" r:id="rId4"/>
+    <hyperlink ref="A6" r:id="rId5"/>
+    <hyperlink ref="A7" r:id="rId6"/>
+    <hyperlink ref="A8" r:id="rId7"/>
+    <hyperlink ref="A9" r:id="rId8"/>
+    <hyperlink ref="A10" r:id="rId9"/>
+    <hyperlink ref="A11" r:id="rId10"/>
+    <hyperlink ref="A12" r:id="rId11"/>
+    <hyperlink ref="A13" r:id="rId12"/>
+    <hyperlink ref="A14" r:id="rId13"/>
+    <hyperlink ref="A15" r:id="rId14"/>
+    <hyperlink ref="A16" r:id="rId15"/>
+    <hyperlink ref="A17" r:id="rId16"/>
+    <hyperlink ref="A18" r:id="rId17"/>
+    <hyperlink ref="A19" r:id="rId18"/>
+    <hyperlink ref="A20" r:id="rId19"/>
+    <hyperlink ref="A21" r:id="rId20"/>
+    <hyperlink ref="A22" r:id="rId21"/>
+    <hyperlink ref="A23" r:id="rId22"/>
+    <hyperlink ref="A24" r:id="rId23"/>
+    <hyperlink ref="A25" r:id="rId24"/>
+    <hyperlink ref="A26" r:id="rId25"/>
+    <hyperlink ref="A27" r:id="rId26"/>
+    <hyperlink ref="A28" r:id="rId27"/>
+    <hyperlink ref="A29" r:id="rId28"/>
+    <hyperlink ref="A30" r:id="rId29"/>
+    <hyperlink ref="A31" r:id="rId30"/>
+    <hyperlink ref="A32" r:id="rId31"/>
+    <hyperlink ref="A33" r:id="rId32"/>
+    <hyperlink ref="A34" r:id="rId33"/>
+    <hyperlink ref="A35" r:id="rId34"/>
+    <hyperlink ref="A36" r:id="rId35"/>
+    <hyperlink ref="A37" r:id="rId36"/>
+    <hyperlink ref="A38" r:id="rId37"/>
+    <hyperlink ref="A39" r:id="rId38"/>
+    <hyperlink ref="A40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>